--- a/artfynd/A 65282-2019 artfynd.xlsx
+++ b/artfynd/A 65282-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123312396</v>
       </c>
       <c r="B2" t="n">
-        <v>57428</v>
+        <v>57431</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 65282-2019 artfynd.xlsx
+++ b/artfynd/A 65282-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123312396</v>
       </c>
       <c r="B2" t="n">
-        <v>57431</v>
+        <v>57437</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 65282-2019 artfynd.xlsx
+++ b/artfynd/A 65282-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123312396</v>
       </c>
       <c r="B2" t="n">
-        <v>57437</v>
+        <v>57440</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 65282-2019 artfynd.xlsx
+++ b/artfynd/A 65282-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123312396</v>
       </c>
       <c r="B2" t="n">
-        <v>57440</v>
+        <v>57441</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 65282-2019 artfynd.xlsx
+++ b/artfynd/A 65282-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -796,6 +796,224 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126259545</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hällsgölsbäcken, Ög</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>517227</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6493971</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Kristberg</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Peter Berry</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Peter Berry</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126259544</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58367</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hällsgölsbäcken, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>517227</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6493971</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Kristberg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Peter Berry</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Peter Berry</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 65282-2019 artfynd.xlsx
+++ b/artfynd/A 65282-2019 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>126259545</v>
       </c>
       <c r="B3" t="n">
-        <v>58327</v>
+        <v>58331</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>126259544</v>
       </c>
       <c r="B4" t="n">
-        <v>58367</v>
+        <v>58371</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 65282-2019 artfynd.xlsx
+++ b/artfynd/A 65282-2019 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>126259545</v>
       </c>
       <c r="B3" t="n">
-        <v>58331</v>
+        <v>58334</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>126259544</v>
       </c>
       <c r="B4" t="n">
-        <v>58371</v>
+        <v>58374</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
